--- a/data/pairing/a_valider_2021.xlsx
+++ b/data/pairing/a_valider_2021.xlsx
@@ -720,10 +720,10 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Congo | 2018 = -4,8
-Congo | 2019 = -0,1
-Congo | 2020 = -7,9
-Congo | 2021(e) = -1,2
+          <t>République du Congo | 2018 = -4,8
+République du Congo | 2019 = -0,1
+République du Congo | 2020 = -7,9
+République du Congo | 2021(e) = -1,2
 Gabon | 2018 = 0,8
 Gabon | 2019 = 3,9
 Gabon | 2020 = -1,8
